--- a/src/Tests/CellsTests.AppendCellDecimal.verified.xlsx
+++ b/src/Tests/CellsTests.AppendCellDecimal.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId4"/>
   </sheets>
   <definedNames/>
   <calcPr fullCalcOnLoad="1"/>
